--- a/study_case_model/scenario_variables/demand_scenarios188.xlsx
+++ b/study_case_model/scenario_variables/demand_scenarios188.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E161"/>
+  <dimension ref="A1:E145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>14362.67807379212</v>
+        <v>28725.35614758425</v>
       </c>
     </row>
     <row r="3">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>14362.67807379212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -527,16 +527,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>23963.01774121611</v>
       </c>
     </row>
     <row r="6">
@@ -553,11 +553,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23963.01774121611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -574,7 +574,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -590,16 +590,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>14928.8320178776</v>
       </c>
     </row>
     <row r="9">
@@ -611,12 +611,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -632,16 +632,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17914.59842145312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -658,11 +658,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>29138.17913844815</v>
       </c>
     </row>
     <row r="12">
@@ -679,11 +679,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5971.532807151039</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -700,11 +700,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5971.532807151039</v>
+        <v>7284.544784612039</v>
       </c>
     </row>
     <row r="14">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>72845.44784612038</v>
+        <v>46487.69937914996</v>
       </c>
     </row>
     <row r="15">
@@ -779,16 +779,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>11621.98641144057</v>
       </c>
     </row>
     <row r="18">
@@ -805,11 +805,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11621.92484478749</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -826,7 +826,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -838,20 +838,20 @@
         <v>2</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>36844.09611630544</v>
       </c>
     </row>
     <row r="21">
@@ -859,16 +859,16 @@
         <v>2</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -889,11 +889,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>11621.98641144057</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -905,16 +905,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>11621.98641144057</v>
+        <v>30755.76046864681</v>
       </c>
     </row>
     <row r="24">
@@ -926,12 +926,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -947,12 +947,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -968,7 +968,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>36844.09611630544</v>
+        <v>10739.47105274393</v>
       </c>
     </row>
     <row r="27">
@@ -989,7 +989,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1031,16 +1031,16 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>23255.36026151579</v>
       </c>
     </row>
     <row r="30">
@@ -1057,11 +1057,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>18453.45628118809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1078,11 +1078,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>5813.840065378947</v>
       </c>
     </row>
     <row r="32">
@@ -1094,16 +1094,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6151.152093729364</v>
+        <v>43048.73460781306</v>
       </c>
     </row>
     <row r="33">
@@ -1115,16 +1115,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6151.152093729364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1141,11 +1141,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>42957.88421097572</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1157,16 +1157,16 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>10753.51342411154</v>
       </c>
     </row>
     <row r="36">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1216,11 +1216,11 @@
         <v>2</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>14534.60016344737</v>
+        <v>26814.71703674526</v>
       </c>
     </row>
     <row r="39">
@@ -1237,11 +1237,11 @@
         <v>2</v>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1258,11 +1258,11 @@
         <v>2</v>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1279,20 +1279,20 @@
         <v>2</v>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>10650.39816506652</v>
       </c>
     </row>
     <row r="42">
@@ -1304,16 +1304,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>10762.18365195327</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1325,16 +1325,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>10762.18365195327</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1346,16 +1346,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>6031.558128076127</v>
       </c>
     </row>
     <row r="45">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1388,16 +1388,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>21507.02684822307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1409,16 +1409,16 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>16626.27482455417</v>
       </c>
     </row>
     <row r="48">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1451,16 +1451,16 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>4156.568706138542</v>
       </c>
     </row>
     <row r="50">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>16088.83022204715</v>
+        <v>34807.53319498364</v>
       </c>
     </row>
     <row r="51">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5362.943407349052</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1535,16 +1535,16 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5362.943407349052</v>
+        <v>13678.42749723228</v>
       </c>
     </row>
     <row r="54">
@@ -1556,16 +1556,16 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>21300.79633013303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1594,20 +1594,20 @@
         <v>2</v>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>18189.81943359092</v>
       </c>
     </row>
     <row r="57">
@@ -1615,16 +1615,16 @@
         <v>2</v>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1636,20 +1636,20 @@
         <v>2</v>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6031.558128076127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1657,20 +1657,20 @@
         <v>2</v>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>14407.72223998532</v>
       </c>
     </row>
     <row r="60">
@@ -1678,16 +1678,16 @@
         <v>2</v>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1699,16 +1699,16 @@
         <v>2</v>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>10391.42176534635</v>
+        <v>17996.18288345583</v>
       </c>
     </row>
     <row r="63">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>10391.42176534635</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1787,16 +1787,16 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>18645.34219708079</v>
       </c>
     </row>
     <row r="66">
@@ -1808,16 +1808,16 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>17403.76659749182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1829,16 +1829,16 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>4661.335549270197</v>
       </c>
     </row>
     <row r="68">
@@ -1850,16 +1850,16 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>51012.92307031886</v>
       </c>
     </row>
     <row r="69">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -1892,16 +1892,16 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>16414.11299667873</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1913,16 +1913,16 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>7157.194301699537</v>
       </c>
     </row>
     <row r="72">
@@ -1934,16 +1934,16 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5471.370998892911</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1955,16 +1955,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5471.370998892911</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1972,11 +1972,11 @@
         <v>2</v>
       </c>
       <c r="B74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>36379.63886718184</v>
+        <v>20917.12956606113</v>
       </c>
     </row>
     <row r="75">
@@ -1993,11 +1993,11 @@
         <v>2</v>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2014,11 +2014,11 @@
         <v>2</v>
       </c>
       <c r="B76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2035,20 +2035,20 @@
         <v>2</v>
       </c>
       <c r="B77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>25831.91942282399</v>
       </c>
     </row>
     <row r="78">
@@ -2056,20 +2056,20 @@
         <v>2</v>
       </c>
       <c r="B78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>7203.861119992658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2077,16 +2077,16 @@
         <v>2</v>
       </c>
       <c r="B79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -2098,20 +2098,20 @@
         <v>2</v>
       </c>
       <c r="B80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>8183.774084666365</v>
       </c>
     </row>
     <row r="81">
@@ -2119,16 +2119,16 @@
         <v>2</v>
       </c>
       <c r="B81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2144,16 +2144,16 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>17996.18288345583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2165,16 +2165,16 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>17996.18288345583</v>
+        <v>22254.18811007404</v>
       </c>
     </row>
     <row r="84">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -2207,16 +2207,16 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>5563.547027518509</v>
       </c>
     </row>
     <row r="86">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>23306.67774635098</v>
+        <v>40990.41965121793</v>
       </c>
     </row>
     <row r="87">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2291,16 +2291,16 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>11406.14843827521</v>
       </c>
     </row>
     <row r="90">
@@ -2312,16 +2312,16 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>15303.87692109566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -2350,20 +2350,20 @@
         <v>2</v>
       </c>
       <c r="B92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5101.292307031887</v>
+        <v>20487.20040827952</v>
       </c>
     </row>
     <row r="93">
@@ -2371,20 +2371,20 @@
         <v>2</v>
       </c>
       <c r="B93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5101.292307031887</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2392,20 +2392,20 @@
         <v>2</v>
       </c>
       <c r="B94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>28628.77720679815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -2413,20 +2413,20 @@
         <v>2</v>
       </c>
       <c r="B95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>38892.08638381703</v>
       </c>
     </row>
     <row r="96">
@@ -2434,16 +2434,16 @@
         <v>2</v>
       </c>
       <c r="B96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -2455,16 +2455,16 @@
         <v>2</v>
       </c>
       <c r="B97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -2476,11 +2476,11 @@
         <v>2</v>
       </c>
       <c r="B98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>10458.56478303056</v>
+        <v>12449.38540723275</v>
       </c>
     </row>
     <row r="99">
@@ -2497,11 +2497,11 @@
         <v>2</v>
       </c>
       <c r="B99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2518,11 +2518,11 @@
         <v>2</v>
       </c>
       <c r="B100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2539,20 +2539,20 @@
         <v>2</v>
       </c>
       <c r="B101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>13653.7344262646</v>
       </c>
     </row>
     <row r="102">
@@ -2564,16 +2564,16 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>12915.959711412</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2585,16 +2585,16 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>12915.959711412</v>
+        <v>3413.43360656615</v>
       </c>
     </row>
     <row r="104">
@@ -2606,16 +2606,16 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>62338.17368154784</v>
       </c>
     </row>
     <row r="105">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -2648,16 +2648,16 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>16367.54816933273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -2669,16 +2669,16 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>7921.836312608667</v>
       </c>
     </row>
     <row r="108">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -2728,11 +2728,11 @@
         <v>2</v>
       </c>
       <c r="B110" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>16690.64108255552</v>
+        <v>26566.47696253567</v>
       </c>
     </row>
     <row r="111">
@@ -2749,11 +2749,11 @@
         <v>2</v>
       </c>
       <c r="B111" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2770,11 +2770,11 @@
         <v>2</v>
       </c>
       <c r="B112" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5563.547027518509</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2791,20 +2791,20 @@
         <v>2</v>
       </c>
       <c r="B113" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5563.547027518509</v>
+        <v>10302.47407090168</v>
       </c>
     </row>
     <row r="114">
@@ -2812,20 +2812,20 @@
         <v>2</v>
       </c>
       <c r="B114" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>40990.41965121793</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2833,16 +2833,16 @@
         <v>2</v>
       </c>
       <c r="B115" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -2854,20 +2854,20 @@
         <v>2</v>
       </c>
       <c r="B116" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>7519.302316630885</v>
       </c>
     </row>
     <row r="117">
@@ -2875,16 +2875,16 @@
         <v>2</v>
       </c>
       <c r="B117" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -2896,20 +2896,20 @@
         <v>2</v>
       </c>
       <c r="B118" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>11406.14843827521</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2917,20 +2917,20 @@
         <v>2</v>
       </c>
       <c r="B119" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>21181.16741521474</v>
       </c>
     </row>
     <row r="120">
@@ -2938,16 +2938,16 @@
         <v>2</v>
       </c>
       <c r="B120" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -2959,20 +2959,20 @@
         <v>2</v>
       </c>
       <c r="B121" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>5295.291853803686</v>
       </c>
     </row>
     <row r="122">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>10243.60020413976</v>
+        <v>61076.99869993115</v>
       </c>
     </row>
     <row r="123">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>10243.60020413976</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3047,16 +3047,16 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>13142.63105446239</v>
       </c>
     </row>
     <row r="126">
@@ -3068,16 +3068,16 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>38892.08638381703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -3106,20 +3106,20 @@
         <v>2</v>
       </c>
       <c r="B128" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>24132.63788208819</v>
       </c>
     </row>
     <row r="129">
@@ -3127,16 +3127,16 @@
         <v>2</v>
       </c>
       <c r="B129" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>EMDEN</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -3148,20 +3148,20 @@
         <v>2</v>
       </c>
       <c r="B130" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>ZEEBRUGGE</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>14939.2624886793</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -3169,20 +3169,20 @@
         <v>2</v>
       </c>
       <c r="B131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>22741.72228308033</v>
       </c>
     </row>
     <row r="132">
@@ -3190,20 +3190,20 @@
         <v>2</v>
       </c>
       <c r="B132" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4979.754162893099</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -3211,20 +3211,20 @@
         <v>2</v>
       </c>
       <c r="B133" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>DORNUM</t>
+          <t>EMDEN</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4979.754162893099</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -3232,11 +3232,11 @@
         <v>2</v>
       </c>
       <c r="B134" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>34134.3360656615</v>
+        <v>6955.542536122148</v>
       </c>
     </row>
     <row r="135">
@@ -3253,11 +3253,11 @@
         <v>2</v>
       </c>
       <c r="B135" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3274,11 +3274,11 @@
         <v>2</v>
       </c>
       <c r="B136" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>ST.FERGUS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3295,20 +3295,20 @@
         <v>2</v>
       </c>
       <c r="B137" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>DUNKERQUE</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>15680.93474963175</v>
       </c>
     </row>
     <row r="138">
@@ -3316,20 +3316,20 @@
         <v>2</v>
       </c>
       <c r="B138" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>15584.54342038696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -3337,20 +3337,20 @@
         <v>2</v>
       </c>
       <c r="B139" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DORNUM</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>3920.233687407937</v>
       </c>
     </row>
     <row r="140">
@@ -3358,20 +3358,20 @@
         <v>2</v>
       </c>
       <c r="B140" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>43090.41843560319</v>
       </c>
     </row>
     <row r="141">
@@ -3379,16 +3379,16 @@
         <v>2</v>
       </c>
       <c r="B141" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>EASINGTON</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -3404,16 +3404,16 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>DUNKERQUE</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Equinor Energy AS</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>7921.836312608667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -3425,16 +3425,16 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>SHELL</t>
+          <t>Equinor Energy AS</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>7921.836312608667</v>
+        <v>16464.20834832093</v>
       </c>
     </row>
     <row r="144">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Vår Energi ASA</t>
+          <t>SHELL</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -3467,351 +3467,15 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ZEEBRUGGE</t>
+          <t>EASINGTON</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Aker BP ASA</t>
+          <t>Vår Energi ASA</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>2</v>
-      </c>
-      <c r="B146" t="n">
-        <v>8</v>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>EMDEN</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Equinor Energy AS</t>
-        </is>
-      </c>
-      <c r="E146" t="n">
-        <v>26566.47696253567</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>2</v>
-      </c>
-      <c r="B147" t="n">
-        <v>8</v>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>EMDEN</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>SHELL</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>2</v>
-      </c>
-      <c r="B148" t="n">
-        <v>8</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>EMDEN</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Vår Energi ASA</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>2</v>
-      </c>
-      <c r="B149" t="n">
-        <v>8</v>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>EMDEN</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Aker BP ASA</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>2</v>
-      </c>
-      <c r="B150" t="n">
-        <v>8</v>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>DORNUM</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Equinor Energy AS</t>
-        </is>
-      </c>
-      <c r="E150" t="n">
-        <v>6181.48444254101</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>2</v>
-      </c>
-      <c r="B151" t="n">
-        <v>8</v>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>DORNUM</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>SHELL</t>
-        </is>
-      </c>
-      <c r="E151" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>2</v>
-      </c>
-      <c r="B152" t="n">
-        <v>8</v>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>DORNUM</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Vår Energi ASA</t>
-        </is>
-      </c>
-      <c r="E152" t="n">
-        <v>2060.494814180337</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>2</v>
-      </c>
-      <c r="B153" t="n">
-        <v>8</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>DORNUM</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Aker BP ASA</t>
-        </is>
-      </c>
-      <c r="E153" t="n">
-        <v>2060.494814180337</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>2</v>
-      </c>
-      <c r="B154" t="n">
-        <v>8</v>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>DUNKERQUE</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Equinor Energy AS</t>
-        </is>
-      </c>
-      <c r="E154" t="n">
-        <v>30077.20926652354</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>2</v>
-      </c>
-      <c r="B155" t="n">
-        <v>8</v>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>DUNKERQUE</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>SHELL</t>
-        </is>
-      </c>
-      <c r="E155" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>2</v>
-      </c>
-      <c r="B156" t="n">
-        <v>8</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>DUNKERQUE</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Vår Energi ASA</t>
-        </is>
-      </c>
-      <c r="E156" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>2</v>
-      </c>
-      <c r="B157" t="n">
-        <v>8</v>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>DUNKERQUE</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Aker BP ASA</t>
-        </is>
-      </c>
-      <c r="E157" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>2</v>
-      </c>
-      <c r="B158" t="n">
-        <v>8</v>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>EASINGTON</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Equinor Energy AS</t>
-        </is>
-      </c>
-      <c r="E158" t="n">
-        <v>13238.22963450921</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>2</v>
-      </c>
-      <c r="B159" t="n">
-        <v>8</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>EASINGTON</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>SHELL</t>
-        </is>
-      </c>
-      <c r="E159" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>2</v>
-      </c>
-      <c r="B160" t="n">
-        <v>8</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>EASINGTON</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Vår Energi ASA</t>
-        </is>
-      </c>
-      <c r="E160" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>2</v>
-      </c>
-      <c r="B161" t="n">
-        <v>8</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>EASINGTON</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Aker BP ASA</t>
-        </is>
-      </c>
-      <c r="E161" t="n">
         <v>0</v>
       </c>
     </row>
